--- a/data/trans_dic/IMC_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,81; 31,71</t>
+          <t>24,13; 31,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,25; 36,4</t>
+          <t>27,58; 36,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,19; 30,13</t>
+          <t>21,02; 29,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,12; 41,45</t>
+          <t>25,32; 41,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,39; 17,56</t>
+          <t>11,27; 17,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,1; 24,68</t>
+          <t>16,97; 25,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 27,32</t>
+          <t>18,3; 26,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,0; 29,04</t>
+          <t>17,03; 29,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 23,9</t>
+          <t>18,94; 23,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,67; 29,55</t>
+          <t>23,56; 29,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 27,18</t>
+          <t>21,01; 27,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,12; 34,11</t>
+          <t>22,88; 34,81</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,41; 49,81</t>
+          <t>42,49; 49,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,9; 56,79</t>
+          <t>48,63; 56,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,0; 48,96</t>
+          <t>41,02; 49,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,96; 57,5</t>
+          <t>45,37; 57,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,47; 30,97</t>
+          <t>23,34; 30,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,62; 42,72</t>
+          <t>34,27; 42,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,33; 42,38</t>
+          <t>34,59; 42,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,88; 63,97</t>
+          <t>35,84; 66,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,64; 40,12</t>
+          <t>34,82; 40,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,02; 48,84</t>
+          <t>43,14; 48,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,99; 44,68</t>
+          <t>39,01; 44,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,92; 62,11</t>
+          <t>43,02; 61,12</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,24; 68,55</t>
+          <t>60,41; 68,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,15; 74,45</t>
+          <t>67,12; 74,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,54; 65,32</t>
+          <t>57,65; 65,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,62; 61,52</t>
+          <t>52,52; 61,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,49; 43,06</t>
+          <t>35,64; 42,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,07; 53,17</t>
+          <t>45,33; 53,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,9; 47,43</t>
+          <t>39,23; 47,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,73; 42,58</t>
+          <t>35,74; 42,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,64; 54,45</t>
+          <t>48,78; 54,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56,97; 62,62</t>
+          <t>56,96; 62,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,92; 55,28</t>
+          <t>49,86; 55,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,98; 50,83</t>
+          <t>45,24; 50,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,31; 75,42</t>
+          <t>67,21; 75,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,17; 79,28</t>
+          <t>72,19; 79,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,72; 73,45</t>
+          <t>66,28; 73,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67,73; 90,61</t>
+          <t>67,33; 90,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,24; 59,86</t>
+          <t>51,02; 60,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,21; 61,48</t>
+          <t>53,67; 62,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,48; 58,42</t>
+          <t>50,14; 58,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,4; 55,63</t>
+          <t>48,92; 55,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,74; 66,75</t>
+          <t>60,62; 66,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63,84; 69,7</t>
+          <t>63,57; 69,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59,46; 65,0</t>
+          <t>59,34; 64,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,75; 79,77</t>
+          <t>59,47; 79,17</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,43; 81,54</t>
+          <t>73,45; 81,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,97; 80,61</t>
+          <t>71,89; 80,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,04; 79,82</t>
+          <t>71,05; 79,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,83; 78,81</t>
+          <t>71,58; 78,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,79; 73,24</t>
+          <t>63,71; 73,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,15; 76,21</t>
+          <t>67,36; 76,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,86; 74,12</t>
+          <t>65,14; 73,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,62; 64,89</t>
+          <t>58,17; 64,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69,7; 76,38</t>
+          <t>69,77; 76,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,25; 77,37</t>
+          <t>71,17; 77,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68,77; 75,31</t>
+          <t>69,22; 75,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,23; 70,87</t>
+          <t>66,11; 70,73</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,74; 80,09</t>
+          <t>69,96; 80,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,85; 88,99</t>
+          <t>79,54; 88,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77,39; 85,96</t>
+          <t>77,09; 85,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72,18; 79,33</t>
+          <t>71,96; 79,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74,03; 82,55</t>
+          <t>73,93; 82,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,65; 85,51</t>
+          <t>76,5; 85,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,3; 77,48</t>
+          <t>67,39; 77,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,65; 92,62</t>
+          <t>69,58; 93,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73,34; 80,19</t>
+          <t>73,7; 80,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79,77; 86,04</t>
+          <t>79,59; 85,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,48; 80,46</t>
+          <t>73,49; 80,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72,33; 88,89</t>
+          <t>72,22; 88,34</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,33; 81,14</t>
+          <t>70,19; 81,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74,06; 84,63</t>
+          <t>73,97; 84,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70,49; 81,06</t>
+          <t>70,39; 80,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66,71; 75,6</t>
+          <t>66,73; 75,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,54; 84,03</t>
+          <t>74,04; 83,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,33; 84,51</t>
+          <t>75,85; 84,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,85; 79,76</t>
+          <t>69,19; 80,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,68; 75,61</t>
+          <t>68,79; 75,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>73,99; 81,43</t>
+          <t>74,27; 81,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76,26; 83,03</t>
+          <t>76,22; 83,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71,71; 79,04</t>
+          <t>71,26; 78,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,74; 74,33</t>
+          <t>69,01; 74,35</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>57,66; 61,05</t>
+          <t>57,54; 61,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63,66; 67,09</t>
+          <t>63,67; 67,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,13; 62,53</t>
+          <t>59,01; 62,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61,42; 73,38</t>
+          <t>61,45; 72,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,43; 49,1</t>
+          <t>45,47; 48,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,57; 56,01</t>
+          <t>52,54; 56,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,56; 54,04</t>
+          <t>50,48; 54,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>51,31; 63,51</t>
+          <t>51,6; 63,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,82; 54,35</t>
+          <t>51,98; 54,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58,58; 61,05</t>
+          <t>58,7; 61,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55,26; 57,7</t>
+          <t>55,08; 57,64</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>57,11; 65,2</t>
+          <t>57,2; 65,83</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad</t>
+          <t>Población con sobrepeso u obesidad (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>116014; 154524</t>
+          <t>117600; 155566</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122416; 163529</t>
+          <t>123890; 163050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85780; 121943</t>
+          <t>85083; 121219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99369; 163943</t>
+          <t>100155; 165169</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53041; 81751</t>
+          <t>52450; 81810</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72323; 104403</t>
+          <t>71794; 105746</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70786; 104455</t>
+          <t>69962; 101690</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51731; 88339</t>
+          <t>51805; 88444</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>177484; 227757</t>
+          <t>180472; 227791</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>206458; 257720</t>
+          <t>205508; 257210</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>166984; 213886</t>
+          <t>165321; 213366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>161805; 238666</t>
+          <t>160085; 243570</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>309640; 363665</t>
+          <t>310233; 363296</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>333607; 387420</t>
+          <t>331755; 384660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>235908; 281660</t>
+          <t>236007; 284367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>189822; 242769</t>
+          <t>191548; 244224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>145870; 192445</t>
+          <t>145077; 189779</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>205628; 253781</t>
+          <t>203547; 253938</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>185532; 229058</t>
+          <t>186954; 229848</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>181665; 323862</t>
+          <t>181456; 334490</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>468235; 542306</t>
+          <t>470564; 542997</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>549084; 623314</t>
+          <t>550525; 625036</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>435062; 498540</t>
+          <t>435246; 501354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>398534; 576658</t>
+          <t>399391; 567521</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>389499; 436021</t>
+          <t>384220; 435121</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>447812; 496473</t>
+          <t>447596; 493665</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>376564; 427519</t>
+          <t>377340; 427416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279873; 327227</t>
+          <t>279374; 327671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>243763; 295748</t>
+          <t>244784; 295002</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>311051; 366885</t>
+          <t>312794; 365711</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>254527; 302592</t>
+          <t>250242; 299861</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>192162; 229019</t>
+          <t>192249; 229429</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>643444; 720331</t>
+          <t>645248; 718112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>773025; 849724</t>
+          <t>772881; 847907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>645174; 714454</t>
+          <t>644448; 715972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>481213; 543787</t>
+          <t>484000; 542911</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>347521; 389354</t>
+          <t>347003; 391452</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>436194; 479185</t>
+          <t>436334; 482034</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>412066; 460498</t>
+          <t>415539; 461311</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>594840; 795819</t>
+          <t>591369; 796385</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>260148; 303909</t>
+          <t>259036; 305712</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>318341; 367818</t>
+          <t>321073; 372100</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>316204; 365969</t>
+          <t>314095; 367948</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>326950; 368205</t>
+          <t>323785; 366716</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>621933; 683454</t>
+          <t>620689; 683585</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>767778; 838212</t>
+          <t>764474; 836575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>745294; 814719</t>
+          <t>743765; 812113</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>920246; 1228610</t>
+          <t>915938; 1219364</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>281875; 313004</t>
+          <t>281962; 312959</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>301823; 338051</t>
+          <t>301492; 337665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>329461; 370185</t>
+          <t>329536; 367299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>392246; 430398</t>
+          <t>390930; 429981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>251975; 289266</t>
+          <t>251644; 289393</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>293060; 332617</t>
+          <t>293982; 333595</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>307361; 351197</t>
+          <t>308651; 350161</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>311192; 344469</t>
+          <t>308788; 343156</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542901; 594884</t>
+          <t>543397; 593032</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>609751; 662102</t>
+          <t>609037; 661445</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>644794; 706136</t>
+          <t>649037; 709175</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>713330; 763274</t>
+          <t>712010; 761787</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>203121; 229971</t>
+          <t>200873; 230114</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>242198; 269930</t>
+          <t>241260; 269807</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>246203; 273465</t>
+          <t>245256; 272857</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>257670; 283213</t>
+          <t>256891; 282442</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>251412; 280350</t>
+          <t>251099; 278485</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>252095; 281246</t>
+          <t>251591; 282173</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>233867; 269252</t>
+          <t>234164; 269758</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>408911; 543764</t>
+          <t>408518; 547762</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>459638; 502574</t>
+          <t>461910; 502850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>504299; 543971</t>
+          <t>503206; 542927</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>489105; 535536</t>
+          <t>489141; 533826</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>682833; 839141</t>
+          <t>681770; 833963</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>143001; 164989</t>
+          <t>142723; 165648</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>173989; 198829</t>
+          <t>173777; 198860</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162454; 186802</t>
+          <t>162225; 186266</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>178266; 202022</t>
+          <t>178316; 202267</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>236085; 266148</t>
+          <t>234518; 264475</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>253752; 284671</t>
+          <t>255519; 283352</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>229823; 266241</t>
+          <t>230934; 267026</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>255424; 281223</t>
+          <t>255835; 280106</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>384777; 423504</t>
+          <t>386254; 425867</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>436059; 474753</t>
+          <t>435829; 476068</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>404643; 445978</t>
+          <t>402086; 445650</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>439363; 475094</t>
+          <t>441057; 475222</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1870667; 1980387</t>
+          <t>1866586; 1979827</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2139359; 2254473</t>
+          <t>2139579; 2253686</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1935748; 2047170</t>
+          <t>1932044; 2043113</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2087287; 2493642</t>
+          <t>2088119; 2474728</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1514167; 1636648</t>
+          <t>1515368; 1632779</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1791319; 1908600</t>
+          <t>1790187; 1912198</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1690039; 1806197</t>
+          <t>1687084; 1809568</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1795803; 2223087</t>
+          <t>1806140; 2215162</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3408281; 3574539</t>
+          <t>3418548; 3579984</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3964416; 4131460</t>
+          <t>3972883; 4136184</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656367; 3817441</t>
+          <t>3644058; 3813354</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3939613; 4497479</t>
+          <t>3946098; 4540917</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,13; 31,92</t>
+          <t>23,78; 31,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,58; 36,3</t>
+          <t>27,29; 36,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,02; 29,95</t>
+          <t>20,82; 30,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,32; 41,76</t>
+          <t>24,06; 40,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 17,57</t>
+          <t>11,1; 17,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,97; 25,0</t>
+          <t>17,1; 24,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,3; 26,6</t>
+          <t>18,78; 26,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,03; 29,07</t>
+          <t>17,57; 28,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,94; 23,91</t>
+          <t>18,66; 23,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,56; 29,49</t>
+          <t>23,67; 29,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,01; 27,11</t>
+          <t>21,02; 27,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,88; 34,81</t>
+          <t>22,56; 32,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,49; 49,76</t>
+          <t>42,64; 50,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,63; 56,38</t>
+          <t>48,47; 56,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,02; 49,43</t>
+          <t>40,65; 49,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,37; 57,85</t>
+          <t>44,59; 56,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,34; 30,54</t>
+          <t>23,49; 30,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,27; 42,75</t>
+          <t>34,54; 42,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,59; 42,53</t>
+          <t>34,46; 42,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,84; 66,07</t>
+          <t>33,78; 42,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,82; 40,17</t>
+          <t>34,49; 39,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,14; 48,98</t>
+          <t>43,21; 48,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,01; 44,93</t>
+          <t>38,8; 44,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,02; 61,12</t>
+          <t>40,81; 48,18</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,41; 68,41</t>
+          <t>60,8; 68,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,12; 74,03</t>
+          <t>67,16; 74,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,65; 65,31</t>
+          <t>57,58; 65,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,52; 61,6</t>
+          <t>52,54; 60,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,64; 42,95</t>
+          <t>35,61; 43,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,33; 53,0</t>
+          <t>45,06; 52,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,23; 47,0</t>
+          <t>39,78; 47,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,74; 42,66</t>
+          <t>38,21; 44,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,78; 54,28</t>
+          <t>48,92; 54,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56,96; 62,49</t>
+          <t>56,74; 62,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,86; 55,4</t>
+          <t>49,79; 55,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45,24; 50,75</t>
+          <t>46,24; 51,57</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,21; 75,82</t>
+          <t>67,37; 75,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,75</t>
+          <t>71,96; 79,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,28; 73,58</t>
+          <t>66,07; 73,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67,33; 90,68</t>
+          <t>66,08; 73,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,02; 60,21</t>
+          <t>51,74; 60,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,67; 62,2</t>
+          <t>53,27; 61,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,14; 58,74</t>
+          <t>50,37; 58,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,92; 55,4</t>
+          <t>48,75; 54,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,62; 66,76</t>
+          <t>60,49; 66,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63,57; 69,56</t>
+          <t>63,91; 69,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59,34; 64,79</t>
+          <t>59,23; 64,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,47; 79,17</t>
+          <t>58,16; 62,97</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,45; 81,52</t>
+          <t>73,7; 81,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,89; 80,52</t>
+          <t>72,22; 80,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,05; 79,2</t>
+          <t>71,01; 79,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,58; 78,73</t>
+          <t>71,78; 78,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,71; 73,27</t>
+          <t>63,57; 73,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,36; 76,44</t>
+          <t>66,97; 76,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,14; 73,9</t>
+          <t>63,94; 73,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,17; 64,64</t>
+          <t>58,81; 65,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69,77; 76,14</t>
+          <t>69,97; 76,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,17; 77,29</t>
+          <t>71,01; 77,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,22; 75,64</t>
+          <t>69,29; 75,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,11; 70,73</t>
+          <t>66,22; 70,86</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,96; 80,14</t>
+          <t>70,53; 80,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,54; 88,95</t>
+          <t>79,85; 88,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77,09; 85,77</t>
+          <t>77,23; 86,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71,96; 79,12</t>
+          <t>70,82; 78,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,93; 82,0</t>
+          <t>73,98; 82,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,5; 85,79</t>
+          <t>76,51; 85,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,39; 77,63</t>
+          <t>68,03; 77,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,58; 93,3</t>
+          <t>67,98; 74,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73,7; 80,23</t>
+          <t>73,84; 80,35</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79,59; 85,88</t>
+          <t>79,45; 85,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73,49; 80,2</t>
+          <t>73,97; 80,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72,22; 88,34</t>
+          <t>70,63; 75,58</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,19; 81,47</t>
+          <t>69,5; 81,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,97; 84,64</t>
+          <t>74,19; 84,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70,39; 80,83</t>
+          <t>70,69; 81,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66,73; 75,69</t>
+          <t>66,08; 75,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,04; 83,5</t>
+          <t>74,12; 83,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,85; 84,12</t>
+          <t>75,62; 84,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,19; 80,0</t>
+          <t>69,13; 80,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,79; 75,31</t>
+          <t>68,96; 75,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74,27; 81,89</t>
+          <t>74,35; 81,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76,22; 83,26</t>
+          <t>75,97; 83,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71,26; 78,98</t>
+          <t>71,17; 79,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,01; 74,35</t>
+          <t>68,8; 74,26</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>57,54; 61,03</t>
+          <t>57,64; 61,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>63,67; 67,07</t>
+          <t>63,75; 67,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,01; 62,41</t>
+          <t>58,94; 62,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61,45; 72,82</t>
+          <t>60,13; 63,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,47; 48,99</t>
+          <t>45,59; 48,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,54; 56,12</t>
+          <t>52,6; 56,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,48; 54,14</t>
+          <t>50,49; 53,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>51,6; 63,29</t>
+          <t>50,07; 53,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,98; 54,43</t>
+          <t>52,04; 54,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58,7; 61,11</t>
+          <t>58,52; 61,0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55,08; 57,64</t>
+          <t>55,19; 57,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>57,2; 65,83</t>
+          <t>55,53; 57,89</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131381</t>
+          <t>124261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68332</t>
+          <t>80453</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>199713</t>
+          <t>204714</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>117600; 155566</t>
+          <t>115875; 153923</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123890; 163050</t>
+          <t>122564; 162696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85083; 121219</t>
+          <t>84273; 121551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100155; 165169</t>
+          <t>95504; 160755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52450; 81810</t>
+          <t>51672; 80499</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71794; 105746</t>
+          <t>72332; 103735</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69962; 101690</t>
+          <t>71782; 102997</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51805; 88444</t>
+          <t>62038; 102236</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>180472; 227791</t>
+          <t>177834; 227682</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205508; 257210</t>
+          <t>206497; 258356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165321; 213366</t>
+          <t>165444; 212830</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>160085; 243570</t>
+          <t>169240; 242272</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219163</t>
+          <t>240045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>232195</t>
+          <t>189106</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>451358</t>
+          <t>429151</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>310233; 363296</t>
+          <t>311323; 368046</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>331755; 384660</t>
+          <t>330649; 382656</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>236007; 284367</t>
+          <t>233850; 282691</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191548; 244224</t>
+          <t>211015; 267572</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>145077; 189779</t>
+          <t>145966; 190183</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>203547; 253938</t>
+          <t>205195; 255044</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>186954; 229848</t>
+          <t>186232; 229571</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>181456; 334490</t>
+          <t>166578; 211714</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>470564; 542997</t>
+          <t>466171; 538553</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>550525; 625036</t>
+          <t>551403; 619013</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>435246; 501354</t>
+          <t>432938; 496072</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>399391; 567521</t>
+          <t>394347; 465566</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302627</t>
+          <t>347446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>210470</t>
+          <t>255484</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>513098</t>
+          <t>602930</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>384220; 435121</t>
+          <t>386684; 437154</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>447596; 493665</t>
+          <t>447888; 493922</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>377340; 427416</t>
+          <t>376861; 427509</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279374; 327671</t>
+          <t>322607; 372716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>244784; 295002</t>
+          <t>244608; 295690</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>312794; 365711</t>
+          <t>310950; 365420</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>250242; 299861</t>
+          <t>253796; 305257</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>192249; 229429</t>
+          <t>235593; 276991</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>645248; 718112</t>
+          <t>647116; 720660</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>772881; 847907</t>
+          <t>769942; 848047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>644448; 715972</t>
+          <t>643451; 716941</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>484000; 542911</t>
+          <t>569071; 634662</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>682433</t>
+          <t>479721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>346980</t>
+          <t>373511</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1029413</t>
+          <t>853232</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>347003; 391452</t>
+          <t>347817; 391418</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>436334; 482034</t>
+          <t>434953; 478626</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>415539; 461311</t>
+          <t>414249; 460363</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>591369; 796385</t>
+          <t>455154; 506245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>259036; 305712</t>
+          <t>262675; 304628</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>321073; 372100</t>
+          <t>318699; 369603</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>314095; 367948</t>
+          <t>315520; 366882</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>323785; 366716</t>
+          <t>349483; 393274</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>620689; 683585</t>
+          <t>619384; 683184</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>764474; 836575</t>
+          <t>768664; 839678</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>743765; 812113</t>
+          <t>742345; 813679</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>915938; 1219364</t>
+          <t>817472; 885122</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>411576</t>
+          <t>443521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>327083</t>
+          <t>365284</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>738658</t>
+          <t>808805</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>281962; 312959</t>
+          <t>282940; 313558</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>301492; 337665</t>
+          <t>302853; 338563</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>329536; 367299</t>
+          <t>329308; 369284</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>390930; 429981</t>
+          <t>424726; 464921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>251644; 289393</t>
+          <t>251075; 288827</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>293982; 333595</t>
+          <t>292288; 332699</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>308651; 350161</t>
+          <t>302966; 348563</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>308788; 343156</t>
+          <t>347082; 383913</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543397; 593032</t>
+          <t>544947; 594295</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>609037; 661445</t>
+          <t>607738; 658950</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>649037; 709175</t>
+          <t>649686; 708986</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>712010; 761787</t>
+          <t>782595; 837523</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270591</t>
+          <t>295798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>475405</t>
+          <t>297246</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>745996</t>
+          <t>593044</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>200873; 230114</t>
+          <t>202499; 230858</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>241260; 269807</t>
+          <t>242207; 269136</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>245256; 272857</t>
+          <t>245683; 273897</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>256891; 282442</t>
+          <t>278936; 308473</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>251099; 278485</t>
+          <t>251262; 280376</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>251591; 282173</t>
+          <t>251637; 280154</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>234164; 269758</t>
+          <t>236401; 270242</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>408518; 547762</t>
+          <t>283133; 309680</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>461910; 502850</t>
+          <t>462809; 503573</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>503206; 542927</t>
+          <t>502268; 543443</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>489141; 533826</t>
+          <t>492359; 536652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>681770; 833963</t>
+          <t>572345; 612436</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>190313</t>
+          <t>207578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>268553</t>
+          <t>293170</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>458866</t>
+          <t>500749</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>142723; 165648</t>
+          <t>141312; 165186</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>173777; 198860</t>
+          <t>174292; 199050</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162225; 186266</t>
+          <t>162898; 186876</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>178316; 202267</t>
+          <t>194052; 220611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>234518; 264475</t>
+          <t>234765; 265387</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>255519; 283352</t>
+          <t>254747; 285308</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>230934; 267026</t>
+          <t>230755; 267693</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>255835; 280106</t>
+          <t>279971; 305408</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>386254; 425867</t>
+          <t>386647; 424864</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>435829; 476068</t>
+          <t>434400; 476528</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>402086; 445650</t>
+          <t>401567; 445738</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>441057; 475222</t>
+          <t>481358; 519559</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2208083</t>
+          <t>2138371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1929019</t>
+          <t>1854255</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4137102</t>
+          <t>3992626</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1866586; 1979827</t>
+          <t>1869898; 1981608</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2139579; 2253686</t>
+          <t>2142227; 2257017</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1932044; 2043113</t>
+          <t>1929506; 2045342</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2088119; 2474728</t>
+          <t>2075818; 2201794</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1515368; 1632779</t>
+          <t>1519462; 1631473</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1790187; 1912198</t>
+          <t>1792324; 1914143</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1687084; 1809568</t>
+          <t>1687468; 1800615</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1806140; 2215162</t>
+          <t>1798777; 1905633</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3418548; 3579984</t>
+          <t>3422415; 3589263</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3972883; 4136184</t>
+          <t>3960643; 4128547</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3644058; 3813354</t>
+          <t>3651727; 3812538</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3946098; 4540917</t>
+          <t>3911796; 4078433</t>
         </is>
       </c>
     </row>
